--- a/Health_Plan_Enrollment_Test_Cases.xlsx
+++ b/Health_Plan_Enrollment_Test_Cases.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H121"/>
+  <dimension ref="A1:H101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,12 +483,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Validate that the system accepts valid prescription medications and displays formulary information</t>
+          <t>Validate that the system accepts valid prescription medications and displays formulary tier and coverage status</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>User is on the medication input page; Formulary database is accessible and up-to-date</t>
+          <t>User is on the medication input page; Formulary database is accessible and populated</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -498,7 +498,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>System validates medication against RxNorm/NCPDP standards; Medication is added to the list; Formulary tier (e.g., Tier 1, Tier 2) is displayed; Coverage status is shown for each available plan</t>
+          <t>System validates medication against RxNorm/NCPDP standards; Medication is added to list; Formulary tier (e.g., Tier 1, Tier 2) is displayed; Coverage status is shown for each available plan</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -525,22 +525,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Validate that system correctly validates medications using approved formulary standards</t>
+          <t>Validate that system correctly validates medications using RxNorm or NCPDP standards</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>User is on medication input page; Multiple formulary standards are configured (RxNorm, NCPDP)</t>
+          <t>User is on medication input page; Multiple formulary standards are configured</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1. Enter medication name that exists in RxNorm 2. Submit medication 3. Verify validation result 4. Enter medication name that exists in NCPDP 5. Submit medication 6. Verify validation result</t>
+          <t>1. Enter medication name 2. System validates against RxNorm standard 3. Enter another medication 4. System validates against NCPDP standard 5. Review validation results</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>System successfully validates medications against both RxNorm and NCPDP standards; Appropriate formulary tier and coverage information is displayed for each medication</t>
+          <t>System successfully validates medications against approved formulary standards; Appropriate tier and coverage information is displayed for each medication</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -572,17 +572,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>User is on medication input page; At least 3 valid medications are available for testing</t>
+          <t>User is on medication input page</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1. Enter first medication name 2. Select from dropdown and add 3. Enter second medication name 4. Select from dropdown and add 5. Enter third medication name 6. Select from dropdown and add 7. Review medication list</t>
+          <t>1. Enter first medication (e.g., Metformin) 2. Click Add 3. Enter second medication (e.g., Atorvastatin) 4. Click Add 5. Enter third medication (e.g., Lisinopril) 6. Click Add 7. Review medication list</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>All three medications are successfully added; Each medication displays its formulary tier; Coverage status is shown for each medication across available plans; User can view complete medication list</t>
+          <t>All three medications are successfully added; Each medication displays formulary tier; Coverage status is shown for each plan; User can view complete medication list</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -604,27 +604,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Verify formulary tier display for different medication tiers</t>
+          <t>Verify medication input with invalid drug name</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Validate that system correctly displays different formulary tiers (Tier 1, 2, 3, 4)</t>
+          <t>Validate system behavior when user enters medication not in formulary database</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>User is on medication input page; Medications from different tiers are available in test data</t>
+          <t>User is on medication input page</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1. Add a Tier 1 medication (generic) 2. Verify tier display 3. Add a Tier 2 medication (preferred brand) 4. Verify tier display 5. Add a Tier 3 medication (non-preferred brand) 6. Verify tier display 7. Add a Tier 4 medication (specialty) 8. Verify tier display</t>
+          <t>1. Enter invalid medication name (e.g., XYZ123Invalid) 2. Attempt to search/add medication 3. Observe system response</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Each medication displays correct formulary tier; Tier information is clearly labeled; Coverage differences across tiers are visible; Cost implications for each tier are indicated</t>
+          <t>System displays appropriate error message indicating medication not found in formulary; User is prompted to verify spelling or contact support; No invalid data is added to profile</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -646,27 +646,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Verify medication coverage status across multiple plans</t>
+          <t>Verify medication input with special characters</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Validate that coverage status is displayed for each medication across different health plans</t>
+          <t>Validate system handling of special characters in medication names</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>User has added at least 2 medications; Multiple health plans are available in the system</t>
+          <t>User is on medication input page</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1. Add first medication to list 2. View coverage status across available plans 3. Add second medication to list 4. View coverage status across available plans 5. Compare coverage between plans</t>
+          <t>1. Enter medication name with special characters (e.g., @#$%^&amp;*) 2. Attempt to add medication 3. Observe system validation</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Coverage status (Covered/Not Covered/Prior Authorization Required) is displayed for each medication; Status is shown for each available plan; Visual indicators clearly differentiate coverage levels; User can easily compare medication coverage across plans</t>
+          <t>System either sanitizes input or displays validation error; No special characters are processed that could cause security issues; Appropriate user guidance is provided</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -688,32 +688,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Verify invalid medication name rejection</t>
+          <t>Verify medication input field with SQL injection attempt</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Validate that system rejects invalid or non-existent medication names</t>
+          <t>Validate system security against SQL injection in medication input</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>User is on medication input page; Formulary validation is active</t>
+          <t>User is on medication input page</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1. Enter invalid medication name (e.g., XYZ123Invalid) 2. Attempt to submit 3. Observe system response</t>
+          <t>1. Enter SQL injection string (e.g., ' OR '1'='1) in medication field 2. Attempt to submit 3. Monitor system response and database logs</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>System displays error message indicating medication not found in formulary; User is prompted to re-enter or select from valid options; No invalid medication is added to the list; Helpful error message guides user to correct input</t>
+          <t>System sanitizes input and prevents SQL injection; Error message or no results displayed; Database remains secure; Security event is logged</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -730,12 +730,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Verify medication input with special characters</t>
+          <t>Verify medication input with empty field</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Validate system handling of special characters in medication names</t>
+          <t>Validate system behavior when medication field is left empty</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1. Enter medication name with special characters (e.g., @#$%^&amp;*) 2. Attempt to submit 3. Observe system response</t>
+          <t>1. Leave medication input field empty 2. Click Add Medication button 3. Observe validation message</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>System either sanitizes input and searches for valid match OR displays appropriate error message; No system errors or crashes occur; User receives clear feedback on acceptable input format</t>
+          <t>System displays validation error message; User is prompted to enter medication name; Empty medication is not added to list</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -772,37 +772,37 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Verify medication input field with SQL injection attempt</t>
+          <t>Verify medication input with maximum character limit</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Validate that medication input field is protected against SQL injection attacks</t>
+          <t>Validate system handling of extremely long medication names</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>User is on medication input page; Security measures are in place</t>
+          <t>User is on medication input page</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1. Enter SQL injection string (e.g., ' OR '1'='1) in medication field 2. Attempt to submit 3. Monitor system behavior and database queries</t>
+          <t>1. Enter medication name exceeding 255 characters 2. Attempt to add medication 3. Observe system behavior</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>System sanitizes input and prevents SQL injection; No unauthorized database access occurs; Error message is displayed or input is rejected; Security logs capture the attempt</t>
+          <t>System either truncates input to maximum allowed length or displays character limit error; Appropriate validation message is shown; System remains stable</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Edge</t>
         </is>
       </c>
     </row>
@@ -814,27 +814,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Verify medication input with extremely long string</t>
+          <t>Verify removal of medication from the list</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Validate system handling of excessively long medication names</t>
+          <t>Validate that users can remove previously added medications</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>User is on medication input page</t>
+          <t>User has added at least one medication to the list</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1. Enter medication name exceeding 500 characters 2. Attempt to submit 3. Observe system response</t>
+          <t>1. View medication list 2. Select medication to remove 3. Click Remove or Delete button 4. Confirm removal 5. Verify medication list</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>System enforces character limit (e.g., 100-200 characters); Appropriate error message is displayed; System remains stable and responsive; User is informed of character limit</t>
+          <t>Selected medication is successfully removed from list; Remaining medications are still displayed; Plan recommendations update based on remaining medications</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Edge</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -856,27 +856,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Verify medication input with empty/null value</t>
+          <t>Verify formulary tier display for Tier 1 medications</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Validate system handling when medication field is left empty</t>
+          <t>Validate correct display of Tier 1 (generic) medication coverage</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>User is on medication input page</t>
+          <t>User is on medication input page; Tier 1 medications exist in formulary</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1. Leave medication input field empty 2. Attempt to submit/add medication 3. Observe system response</t>
+          <t>1. Enter Tier 1 generic medication 2. Add to list 3. Review tier classification 4. Check coverage status across plans</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>System displays validation error message; User is prompted to enter medication name; Empty medication is not added to list; Required field indicator is shown</t>
+          <t>System correctly identifies and displays medication as Tier 1; Lower copay amounts are shown; Coverage status indicates preferred status; All plans show consistent tier classification</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -898,27 +898,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Verify medication list with maximum number of medications</t>
+          <t>Verify formulary tier display for Tier 2 medications</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Validate system behavior when maximum number of medications is reached</t>
+          <t>Validate correct display of Tier 2 (preferred brand) medication coverage</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>User is on medication input page; System has defined maximum medication limit</t>
+          <t>User is on medication input page; Tier 2 medications exist in formulary</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1. Add medications up to system maximum (e.g., 50 medications) 2. Attempt to add one more medication 3. Observe system response</t>
+          <t>1. Enter Tier 2 preferred brand medication 2. Add to list 3. Review tier classification 4. Check coverage status across plans</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>System enforces maximum medication limit; Clear message indicates limit reached; User can still edit or remove existing medications; System performance remains acceptable with maximum medications</t>
+          <t>System correctly identifies and displays medication as Tier 2; Moderate copay amounts are shown; Coverage status is displayed; Tier differences are clear</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Edge</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -940,27 +940,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Verify removal of medication from the list</t>
+          <t>Verify formulary tier display for Tier 3 medications</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Validate that users can successfully remove medications from their list</t>
+          <t>Validate correct display of Tier 3 (non-preferred brand) medication coverage</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>User has added at least 2 medications to the list</t>
+          <t>User is on medication input page; Tier 3 medications exist in formulary</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1. View medication list 2. Select medication to remove 3. Click Remove/Delete button 4. Confirm removal if prompted 5. Verify medication list</t>
+          <t>1. Enter Tier 3 non-preferred brand medication 2. Add to list 3. Review tier classification 4. Check coverage status across plans</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Selected medication is removed from the list; Remaining medications are still displayed; Formulary information updates accordingly; Plan recommendations refresh based on updated medication list</t>
+          <t>System correctly identifies and displays medication as Tier 3; Higher copay amounts are shown; Coverage status indicates non-preferred status; Alternative medications may be suggested</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -982,27 +982,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Verify medication search with partial name</t>
+          <t>Verify medication not covered by any plan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Validate that system supports partial medication name search</t>
+          <t>Validate system behavior when medication is not covered by available plans</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>User is on medication input page; Search functionality is enabled</t>
+          <t>User is on medication input page</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1. Enter partial medication name (e.g., Lisin for Lisinopril) 2. Observe search results 3. Select correct medication from results</t>
+          <t>1. Enter medication not covered by any available plan 2. Add to list 3. Review coverage status</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>System displays relevant medication matches; Autocomplete or dropdown shows matching medications; User can select correct medication from suggestions; Selected medication is validated against formulary</t>
+          <t>System displays clear message indicating medication is not covered; Alternative covered medications may be suggested; User can still proceed with enrollment; Coverage status shows Not Covered for all plans</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -1024,27 +1024,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Verify PCP search with valid provider name</t>
+          <t>Verify medication covered by some but not all plans</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Validate that users can search for and select a Primary Care Provider</t>
+          <t>Validate display when medication coverage varies across plans</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>User is on provider selection page; Provider database is accessible</t>
+          <t>User is on medication input page</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1. Navigate to PCP search section 2. Enter valid PCP name 3. Click Search 4. Review search results 5. Select preferred PCP</t>
+          <t>1. Enter medication covered by only some plans 2. Add to list 3. Review coverage across all plans</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>System displays matching PCPs; Provider information includes name, specialty, location; Network participation status is shown; Acceptance of new patients is indicated; User can select PCP from results</t>
+          <t>System clearly shows which plans cover the medication; Plans with coverage are highlighted or prioritized; Coverage status varies appropriately by plan; User can make informed decision</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1066,27 +1066,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Verify specialist search with valid provider name</t>
+          <t>Verify successful PCP search by name</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Validate that users can search for and select specialist providers</t>
+          <t>Validate that users can search for primary care providers by name</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>User is on provider selection page; Provider database is accessible</t>
+          <t>User is on provider search page; Provider database is accessible</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1. Navigate to specialist search section 2. Select specialty type (e.g., Cardiologist) 3. Enter specialist name 4. Click Search 5. Review search results 6. Select preferred specialist</t>
+          <t>1. Navigate to PCP search section 2. Enter provider name (e.g., Dr. Smith) 3. Click Search 4. Review search results</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>System displays matching specialists; Specialty type is confirmed; Network participation status is shown; Acceptance of new patients is indicated; Plan affiliation is displayed; User can select specialist from results</t>
+          <t>System returns list of matching PCPs; Results show provider name, specialty, location, network status; User can select from results; Search completes within acceptable time</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1108,27 +1108,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Verify provider network participation status display</t>
+          <t>Verify successful PCP search by location</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Validate that current network participation status is accurately displayed for providers</t>
+          <t>Validate that users can search for PCPs by geographic location</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>User is searching for providers; Provider network data is current</t>
+          <t>User is on provider search page</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1. Search for provider 2. View provider details 3. Check network participation status 4. Verify status accuracy against known data</t>
+          <t>1. Navigate to PCP search section 2. Enter ZIP code or city 3. Select search radius 4. Click Search 5. Review results</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Network participation status is clearly displayed (In-Network/Out-of-Network); Status is current and accurate; Visual indicators (icons, colors) differentiate network status; Multiple network affiliations are shown if applicable</t>
+          <t>System returns PCPs within specified location radius; Results are sorted by distance; Provider details include address and contact information; Map view may be available</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1150,27 +1150,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Verify new patient acceptance status display</t>
+          <t>Verify successful specialist search by specialty type</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Validate that provider's acceptance of new patients is clearly indicated</t>
+          <t>Validate that users can search for specialists by medical specialty</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>User is viewing provider search results; Provider acceptance status is available</t>
+          <t>User is on provider search page</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1. Search for providers 2. View search results 3. Check new patient acceptance status for each provider</t>
+          <t>1. Navigate to specialist search section 2. Select specialty from dropdown (e.g., Cardiology) 3. Enter location 4. Click Search 5. Review results</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Acceptance status is clearly displayed (Accepting/Not Accepting New Patients); Status is prominently visible in search results; User can filter by acceptance status; Information is current and accurate</t>
+          <t>System returns specialists matching selected specialty; Results show specialty certification; Network participation status is displayed; User can select preferred specialist</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1192,27 +1192,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Verify provider plan affiliation display</t>
+          <t>Verify provider network participation status display</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Validate that provider's affiliation with selected plans is shown</t>
+          <t>Validate that current network participation status is clearly displayed for each provider</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>User has searched for providers; Multiple plans are available for comparison</t>
+          <t>User has searched for providers</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1. Search for provider 2. View provider details 3. Check plan affiliation information 4. Compare across multiple plans</t>
+          <t>1. Perform provider search 2. Review search results 3. Check network status for each provider 4. Verify status indicators</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Provider's affiliation with each plan is clearly shown; In-network status is indicated per plan; Tier level within network is displayed if applicable; User can easily compare provider availability across plans</t>
+          <t>Each provider shows clear network status (In-Network, Out-of-Network); Status is current and accurate; Visual indicators (icons, colors) distinguish network status; Status is validated in real-time</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1234,27 +1234,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Verify provider search with invalid name</t>
+          <t>Verify provider accepting new patients status</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Validate system handling of invalid or non-existent provider names</t>
+          <t>Validate that system displays whether provider is accepting new patients</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>User is on provider search page</t>
+          <t>User has searched for providers</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1. Enter invalid provider name (e.g., XYZ999Invalid) 2. Click Search 3. Observe system response</t>
+          <t>1. Perform provider search 2. Review provider details 3. Check new patient acceptance status 4. Verify information accuracy</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>System displays message indicating no providers found; User is prompted to refine search criteria; Suggestions for valid search are provided; No system errors occur</t>
+          <t>System clearly indicates if provider is accepting new patients; Status is current (updated within last 30 days); Providers not accepting new patients are marked accordingly; User can filter by this criterion</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -1276,27 +1276,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Verify provider search with empty field</t>
+          <t>Verify provider affiliation with selected plan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Validate system handling when provider search field is left empty</t>
+          <t>Validate that provider affiliation is shown for each plan option</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>User is on provider search page</t>
+          <t>User has selected providers and is viewing plan recommendations</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1. Leave provider search field empty 2. Click Search 3. Observe system response</t>
+          <t>1. Add preferred PCP to profile 2. Add preferred specialist to profile 3. View plan recommendations 4. Check provider affiliation for each plan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>System displays validation error or prompts user to enter search criteria; No search is executed with empty field; User receives clear guidance on required input; System remains stable</t>
+          <t>System shows which plans include selected providers in network; Affiliation status is clear for each plan; Plans with both providers are prioritized; User can easily compare provider coverage</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Verify provider search with special characters</t>
+          <t>Verify provider search with no results</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Validate system handling of special characters in provider search</t>
+          <t>Validate system behavior when provider search returns no matches</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1. Enter provider name with special characters (e.g., O'Brien, Smith-Jones) 2. Click Search 3. Observe results</t>
+          <t>1. Enter provider name that does not exist in database 2. Click Search 3. Observe system response</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>System correctly handles common special characters in names (apostrophes, hyphens); Relevant providers are returned in search results; No system errors occur; Search functionality works as expected</t>
+          <t>System displays message indicating no providers found; User is prompted to modify search criteria; Suggestions for broader search are provided; System remains stable</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Edge</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -1360,27 +1360,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Verify provider search by location/zip code</t>
+          <t>Verify provider search with invalid characters</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Validate that users can search for providers by geographic location</t>
+          <t>Validate system handling of special characters in provider search</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>User is on provider search page; Location-based search is enabled</t>
+          <t>User is on provider search page</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1. Enter zip code or city name 2. Optionally enter provider specialty 3. Click Search 4. Review results</t>
+          <t>1. Enter special characters in provider name field 2. Attempt search 3. Observe system validation</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>System displays providers within specified location; Results are sorted by distance or relevance; Location information is shown for each provider; Map view is available if supported</t>
+          <t>System sanitizes input or displays validation error; No security vulnerabilities are exposed; Appropriate error message guides user; Search does not execute with invalid input</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -1402,27 +1402,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Verify selection of multiple providers (PCP and specialists)</t>
+          <t>Verify provider search with empty fields</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Validate that users can select multiple providers including PCP and specialists</t>
+          <t>Validate system behavior when all search fields are empty</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>User is on provider selection page</t>
+          <t>User is on provider search page</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1. Search and select a PCP 2. Search and select first specialist 3. Search and select second specialist 4. Review selected providers list</t>
+          <t>1. Leave all search fields empty 2. Click Search button 3. Observe validation</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>All selected providers are added to user's profile; Provider types are clearly labeled (PCP, Specialist); Network status is maintained for each provider; User can view complete provider list</t>
+          <t>System displays validation error requiring at least one search criterion; User is prompted to enter search parameters; No search is executed; Clear guidance is provided</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -1444,27 +1444,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Verify removal of selected provider</t>
+          <t>Verify addition of multiple providers to profile</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Validate that users can remove previously selected providers</t>
+          <t>Validate that users can add multiple PCPs and specialists</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>User has selected at least 2 providers</t>
+          <t>User is on provider search page</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1. View selected providers list 2. Select provider to remove 3. Click Remove button 4. Confirm removal if prompted</t>
+          <t>1. Search and add first PCP 2. Search and add second PCP as backup 3. Search and add cardiologist 4. Search and add endocrinologist 5. Review provider list</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Selected provider is removed from list; Remaining providers are still displayed; Plan recommendations update based on remaining providers; System confirms successful removal</t>
+          <t>All providers are successfully added to profile; Provider list shows all selections with details; Network status is displayed for each; User can manage provider list</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1486,37 +1486,37 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Verify provider search with SQL injection attempt</t>
+          <t>Verify removal of provider from profile</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Validate that provider search field is protected against SQL injection</t>
+          <t>Validate that users can remove previously selected providers</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>User is on provider search page; Security measures are in place</t>
+          <t>User has added providers to profile</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1. Enter SQL injection string in provider search field 2. Click Search 3. Monitor system behavior</t>
+          <t>1. View provider list 2. Select provider to remove 3. Click Remove button 4. Confirm removal 5. Verify updated list</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>System sanitizes input and prevents SQL injection; No unauthorized database access occurs; Appropriate error message or no results displayed; Security logs capture the attempt</t>
+          <t>Selected provider is removed from profile; Remaining providers are still displayed; Plan recommendations update based on remaining providers; System confirms removal</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -1528,27 +1528,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Verify monthly premium range input</t>
+          <t>Verify provider out-of-network warning</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Validate that users can specify desired monthly premium range</t>
+          <t>Validate that system warns when selected provider is out-of-network for recommended plans</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>User is on financial preferences page</t>
+          <t>User is selecting providers</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1. Navigate to premium range section 2. Enter minimum premium amount (e.g., $100) 3. Enter maximum premium amount (e.g., $300) 4. Save preferences</t>
+          <t>1. Search for provider 2. Select provider that is out-of-network 3. Add to profile 4. View plan recommendations</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>System accepts valid premium range; Minimum is less than maximum; Range is used to filter plan recommendations; User preferences are saved</t>
+          <t>System displays warning that provider is out-of-network; Impact on costs is explained; Alternative in-network providers may be suggested; User can still proceed with selection</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1570,27 +1570,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Verify deductible amount preference input</t>
+          <t>Verify provider not accepting new patients warning</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Validate that users can specify preferred deductible amount</t>
+          <t>Validate system notification when selected provider is not accepting new patients</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>User is on financial preferences page</t>
+          <t>User is selecting providers</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1. Navigate to deductible preference section 2. Select or enter preferred deductible (e.g., $1000, $2500, $5000) 3. Save preferences</t>
+          <t>1. Search for provider 2. Select provider not accepting new patients 3. Attempt to add to profile</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>System accepts valid deductible preference; Preference is used to filter plan recommendations; User can select from common deductible amounts or enter custom amount; Preferences are saved</t>
+          <t>System displays clear warning message; User is informed of new patient status; Alternative providers may be suggested; User can acknowledge and proceed or select different provider</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Verify out-of-pocket maximum input</t>
+          <t>Verify financial preference input for monthly premium range</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Validate that users can specify acceptable out-of-pocket maximum</t>
+          <t>Validate that users can specify desired monthly premium range</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1627,12 +1627,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1. Navigate to out-of-pocket maximum section 2. Enter acceptable maximum (e.g., $5000) 3. Save preferences</t>
+          <t>1. Navigate to financial preferences section 2. Enter minimum premium amount (e.g., $100) 3. Enter maximum premium amount (e.g., $300) 4. Save preferences</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>System accepts valid out-of-pocket maximum; Value is used to filter plan recommendations; Validation ensures reasonable amount; Preferences are saved</t>
+          <t>System accepts valid premium range; Range is used to filter plan recommendations; Validation ensures minimum is less than maximum; Preferences are saved to user profile</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Verify all financial preferences input together</t>
+          <t>Verify financial preference input for deductible amount</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Validate that users can input all financial preferences in one session</t>
+          <t>Validate that users can specify preferred deductible amount</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1669,12 +1669,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1. Enter monthly premium range ($150-$350) 2. Enter preferred deductible ($2000) 3. Enter out-of-pocket maximum ($6000) 4. Save all preferences</t>
+          <t>1. Navigate to deductible preference section 2. Enter preferred deductible amount (e.g., $1000) 3. Select deductible range tolerance 4. Save preferences</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>All financial preferences are accepted and saved; Values are validated for logical consistency; Preferences are used collectively to filter plans; User can proceed to plan recommendations</t>
+          <t>System accepts valid deductible preference; Preference is used to filter and rank plans; Common deductible amounts may be suggested; Preferences are saved</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1696,12 +1696,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Verify invalid premium range (minimum greater than maximum)</t>
+          <t>Verify financial preference input for out-of-pocket maximum</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Validate system handling when minimum premium exceeds maximum</t>
+          <t>Validate that users can specify acceptable out-of-pocket maximum</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1. Enter minimum premium ($500) 2. Enter maximum premium ($200) 3. Attempt to save</t>
+          <t>1. Navigate to out-of-pocket maximum section 2. Enter maximum acceptable amount (e.g., $5000) 3. Save preferences</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>System displays validation error; User is informed that minimum must be less than maximum; Preferences are not saved until corrected; Clear error message guides user</t>
+          <t>System accepts valid out-of-pocket maximum; Preference filters plan recommendations; Plans exceeding limit are excluded or deprioritized; Preferences are saved</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -1738,12 +1738,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Verify negative values in financial preferences</t>
+          <t>Verify financial preference validation with invalid premium range</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Validate system rejection of negative values in financial fields</t>
+          <t>Validate system behavior when minimum premium exceeds maximum</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1. Enter negative premium amount (e.g., -$100) 2. Attempt to save 3. Observe system response</t>
+          <t>1. Enter minimum premium of $500 2. Enter maximum premium of $200 3. Attempt to save preferences</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>System rejects negative values; Validation error message is displayed; User is prompted to enter positive values; Preferences are not saved with invalid data</t>
+          <t>System displays validation error; User is informed that minimum cannot exceed maximum; Preferences are not saved until corrected; Clear error message guides user</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1780,12 +1780,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Verify non-numeric input in financial fields</t>
+          <t>Verify financial preference with negative values</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Validate system handling of non-numeric input in financial preference fields</t>
+          <t>Validate system handling of negative values in financial inputs</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1. Enter text characters in premium field (e.g., ABC) 2. Attempt to save 3. Observe system response</t>
+          <t>1. Enter negative value for premium (e.g., -$100) 2. Attempt to save 3. Observe validation</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>System displays validation error; User is informed that numeric values are required; Input field may restrict to numeric characters only; Clear error message is shown</t>
+          <t>System rejects negative values; Validation error message is displayed; User is prompted to enter positive values; No negative values are saved</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Verify extremely high financial preference values</t>
+          <t>Verify financial preference with non-numeric input</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Validate system handling of unrealistically high financial values</t>
+          <t>Validate system handling of non-numeric characters in financial fields</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1. Enter extremely high premium ($999999) 2. Enter extremely high deductible ($999999) 3. Attempt to save</t>
+          <t>1. Enter alphabetic characters in premium field (e.g., ABC) 2. Attempt to save 3. Observe validation</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>System either accepts values and returns no matching plans OR enforces reasonable maximum limits; User is informed if values exceed typical plan ranges; System remains stable; Appropriate feedback is provided</t>
+          <t>System displays validation error; Only numeric input is accepted; Field may auto-format to currency; Clear guidance is provided</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Edge</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Verify zero values in financial preferences</t>
+          <t>Verify financial preference with extremely high values</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Validate system handling of zero values in financial fields</t>
+          <t>Validate system handling of unrealistic financial values</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1. Enter $0 for premium range minimum 2. Enter $0 for deductible 3. Attempt to save</t>
+          <t>1. Enter extremely high premium (e.g., $999999999) 2. Attempt to save 3. Observe system behavior</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>System either accepts zero values as valid preferences OR displays validation message; If accepted, plans with lowest costs are prioritized; User receives appropriate feedback; System behavior is consistent with business rules</t>
+          <t>System may display warning about unrealistic values; Maximum reasonable limits may be enforced; User is prompted to verify input; System remains stable</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Verify financial preferences with decimal values</t>
+          <t>Verify financial preference with zero values</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Validate system handling of decimal/cent values in financial fields</t>
+          <t>Validate system handling of zero values in financial preferences</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1. Enter premium with cents ($150.50) 2. Enter deductible with cents ($1000.99) 3. Save preferences</t>
+          <t>1. Enter $0 for premium range 2. Enter $0 for deductible 3. Attempt to save</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>System accepts decimal values OR rounds to nearest dollar; Consistent handling across all financial fields; Saved values match entered values (or rounded values); No calculation errors occur</t>
+          <t>System either accepts zero as valid minimum or displays validation error; Behavior is consistent with business rules; Appropriate messaging guides user; System handles edge case gracefully</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1958,17 +1958,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>User has completed medication, provider, and financial preference inputs; At least 3 plans exist that match criteria</t>
+          <t>User has completed health data and financial preferences input</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1. Complete all required inputs 2. Submit for plan recommendations 3. View recommendations page 4. Count number of plans recommended</t>
+          <t>1. Complete medication input 2. Select preferred providers 3. Enter financial preferences 4. Submit for recommendations 5. View results</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>System displays at least 3 plan recommendations; Plans are personalized based on user inputs; Each plan shows key information; Plans are prioritized/ranked</t>
+          <t>System generates at least three plan recommendations; Plans are personalized based on input data; Recommendations are ranked by relevance; All three plans are displayed clearly</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2000,17 +2000,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>User has entered 3+ medications; Plan recommendations are generated</t>
+          <t>User has entered medications and completed preferences</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1. Review recommended plans 2. Check medication coverage for each plan 3. Verify formulary tier information 4. Compare coverage across plans</t>
+          <t>1. Enter multiple medications 2. Complete other preferences 3. Generate recommendations 4. Review medication coverage in recommended plans</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Recommended plans provide coverage for user's medications; Formulary tier is shown for each medication in each plan; Plans with better medication coverage are prioritized; Coverage gaps are clearly indicated if any</t>
+          <t>Recommended plans provide coverage for entered medications; Plans with better medication coverage are prioritized; Formulary tier and costs are shown for each plan; Alignment with medication needs is demonstrable</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2037,22 +2037,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Validate that recommended plans include user's preferred providers in network</t>
+          <t>Validate that recommended plans include user's preferred providers</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>User has selected PCP and specialists; Plan recommendations are generated</t>
+          <t>User has selected providers and completed preferences</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1. Review recommended plans 2. Check provider network status for each plan 3. Verify selected providers are in-network</t>
+          <t>1. Select preferred PCP and specialists 2. Complete other preferences 3. Generate recommendations 4. Review provider network in recommended plans</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Recommended plans include user's preferred providers in network; Provider network status is clearly shown; Plans with all providers in-network are prioritized; Out-of-network providers are flagged if applicable</t>
+          <t>Recommended plans include selected providers in network; Plans with more selected providers are prioritized; Provider affiliation is clearly shown; Alignment with provider preferences is demonstrable</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2084,17 +2084,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>User has specified premium range, deductible, and OOP max; Plan recommendations are generated</t>
+          <t>User has entered financial preferences</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1. Review recommended plans 2. Check premium amounts against specified range 3. Check deductible amounts against preference 4. Check OOP maximum against specified limit</t>
+          <t>1. Set premium range $100-$300 2. Set deductible preference $1000 3. Set out-of-pocket max $5000 4. Generate recommendations 5. Review plan costs</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Recommended plans fall within specified premium range; Deductibles align with user preference; OOP maximums are within acceptable limit; Plans are ranked by financial fit</t>
+          <t>Recommended plans fall within specified premium range; Deductibles are close to preferred amount; Out-of-pocket maximums do not exceed limit; Financial alignment is demonstrable</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2121,22 +2121,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Validate that plans are prioritized based on best overall match to user needs</t>
+          <t>Validate that plans are ranked by relevance to user needs</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>User has completed all inputs with specific preferences; Multiple plans match criteria</t>
+          <t>User has completed all input sections</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1. Review recommended plans order 2. Analyze why each plan is ranked in its position 3. Verify ranking logic against user inputs</t>
+          <t>1. Enter comprehensive health and financial data 2. Generate recommendations 3. Review ranking order 4. Verify prioritization logic</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Plans are ranked in priority order; Highest priority plans best match user's combined needs; Ranking considers medications, providers, and financial factors; Ranking logic is transparent to user</t>
+          <t>Plans are ranked with most relevant first; Ranking considers medications, providers, and costs; Prioritization logic is transparent; User can understand why plans are ranked as shown</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2158,27 +2158,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Verify plan recommendations when fewer than three plans match</t>
+          <t>Verify plan recommendations when fewer than three plans match criteria</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Validate system behavior when fewer than 3 plans match user criteria</t>
+          <t>Validate system behavior when fewer than three plans meet all criteria</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>User has very specific criteria that only 1-2 plans can meet</t>
+          <t>User has very restrictive preferences</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1. Enter restrictive criteria 2. Submit for recommendations 3. View results</t>
+          <t>1. Enter very specific medication requirements 2. Select rare specialist 3. Set very low premium range 4. Generate recommendations</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>System displays all matching plans even if fewer than 3; User is informed that limited plans match criteria; Suggestions to broaden criteria are provided; System does not force-fit non-matching plans</t>
+          <t>System displays all matching plans even if fewer than three; User is informed of limited options; Suggestions to broaden criteria may be provided; System explains why fewer plans are shown</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2200,27 +2200,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Verify plan recommendations when no plans match criteria</t>
+          <t>Verify plan recommendations with no matching plans</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Validate system behavior when no plans match user's criteria</t>
+          <t>Validate system behavior when no plans match all criteria</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>User has criteria that no plans can satisfy</t>
+          <t>User has incompatible or impossible criteria</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1. Enter criteria that cannot be matched 2. Submit for recommendations 3. View results</t>
+          <t>1. Enter criteria that no plan can satisfy 2. Generate recommendations 3. Observe system response</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>System displays message that no plans match all criteria; Suggestions to adjust criteria are provided; Closest matching plans may be shown with gaps highlighted; User can modify inputs and retry</t>
+          <t>System displays message that no plans match all criteria; Suggestions to modify preferences are provided; Closest matching plans may be shown; User can adjust criteria and retry</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2242,27 +2242,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Verify plan recommendations refresh after input changes</t>
+          <t>Verify side-by-side comparison tool for two plans</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Validate that recommendations update when user modifies inputs</t>
+          <t>Validate comparison functionality with two selected plans</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>User has received initial plan recommendations</t>
+          <t>User has received plan recommendations</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1. View initial recommendations 2. Navigate back to inputs 3. Modify medication or provider selection 4. Resubmit for recommendations 5. Compare new recommendations</t>
+          <t>1. Select first plan for comparison 2. Select second plan for comparison 3. Open comparison tool 4. Review comparison display</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>System generates new recommendations based on updated inputs; Recommendations reflect the changes made; Previous recommendations are replaced; User can see impact of input changes on plan options</t>
+          <t>Comparison tool displays both plans side-by-side; Key differences are highlighted; All comparison categories are shown; Display is clear and easy to read</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2284,27 +2284,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Verify side-by-side comparison tool for two plans</t>
+          <t>Verify side-by-side comparison tool for three plans</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Validate that comparison tool works with two selected plans</t>
+          <t>Validate comparison functionality with maximum three plans</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>User has received plan recommendations; At least 2 plans are available</t>
+          <t>User has received plan recommendations</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1. Select first plan for comparison 2. Select second plan for comparison 3. Open comparison tool 4. Review comparison display</t>
+          <t>1. Select first plan for comparison 2. Select second plan for comparison 3. Select third plan for comparison 4. Open comparison tool 5. Review display</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Comparison tool displays both plans side-by-side; Key attributes are aligned for easy comparison; Differences are highlighted; User can easily scan and compare features</t>
+          <t>Comparison tool displays all three plans side-by-side; Key differences are highlighted across all three; Display remains readable with three columns; User can easily compare all aspects</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2326,27 +2326,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Verify side-by-side comparison tool for three plans</t>
+          <t>Verify comparison tool displays monthly premium differences</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Validate that comparison tool works with maximum three plans</t>
+          <t>Validate that monthly premiums are clearly shown and compared</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>User has received plan recommendations; At least 3 plans are available</t>
+          <t>User has opened comparison tool with multiple plans</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1. Select first plan for comparison 2. Select second plan for comparison 3. Select third plan for comparison 4. Open comparison tool 5. Review comparison display</t>
+          <t>1. Open comparison tool 2. Locate premium section 3. Review premium amounts for each plan 4. Verify difference highlighting</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Comparison tool displays all three plans side-by-side; Layout accommodates three plans clearly; Key attributes are aligned across all three; Differences are highlighted; Comparison remains readable and usable</t>
+          <t>Monthly premium is displayed for each plan; Differences are highlighted or color-coded; Lowest premium may be indicated; Values are accurate and formatted as currency</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2368,27 +2368,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Verify comparison of monthly premiums</t>
+          <t>Verify comparison tool displays deductible differences</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Validate that monthly premiums are clearly compared across plans</t>
+          <t>Validate that deductibles are clearly shown and compared</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>User has opened comparison tool with 2-3 plans selected</t>
+          <t>User has opened comparison tool with multiple plans</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1. View comparison tool 2. Locate monthly premium section 3. Compare premium amounts across plans</t>
+          <t>1. Open comparison tool 2. Locate deductible section 3. Review deductible amounts for each plan 4. Verify difference highlighting</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Monthly premiums are displayed for each plan; Amounts are clearly labeled; Lowest premium is highlighted or indicated; Differences in premium amounts are easy to identify</t>
+          <t>Deductible amount is displayed for each plan; Individual and family deductibles may be shown separately; Differences are highlighted; Lowest deductible may be indicated</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2410,27 +2410,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Verify comparison of deductibles</t>
+          <t>Verify comparison tool displays copay differences</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Validate that deductibles are clearly compared across plans</t>
+          <t>Validate that copays for various services are compared</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>User has opened comparison tool with 2-3 plans selected</t>
+          <t>User has opened comparison tool with multiple plans</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1. View comparison tool 2. Locate deductible section 3. Compare deductible amounts across plans</t>
+          <t>1. Open comparison tool 2. Locate copay section 3. Review copays for different service types 4. Compare across plans</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Deductibles are displayed for each plan; Individual and family deductibles shown if applicable; Lowest deductible is highlighted; Differences are easy to identify</t>
+          <t>Copays are shown for multiple service types (PCP visit, specialist, ER, etc.); Differences are clear across plans; Values are formatted consistently; User can easily identify best copay structure</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2452,27 +2452,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Verify comparison of co-pays</t>
+          <t>Verify comparison tool displays covered services</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Validate that co-pay information is clearly compared across plans</t>
+          <t>Validate that covered services are listed and compared</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>User has opened comparison tool with 2-3 plans selected</t>
+          <t>User has opened comparison tool with multiple plans</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1. View comparison tool 2. Locate co-pay section 3. Compare co-pay amounts for different service types</t>
+          <t>1. Open comparison tool 2. Locate covered services section 3. Review service coverage for each plan 4. Identify differences</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Co-pays for various services are displayed (PCP visit, specialist, ER, etc.); Amounts are aligned across plans; Differences are highlighted; User can easily compare co-pay structures</t>
+          <t>Covered services are listed for each plan; Differences in coverage are highlighted; Services unique to certain plans are indicated; Coverage details are comprehensive</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2494,27 +2494,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Verify comparison of covered services</t>
+          <t>Verify comparison tool displays estimated costs for common services</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Validate that covered services are clearly compared across plans</t>
+          <t>Validate that estimated costs for common healthcare services are shown</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>User has opened comparison tool with 2-3 plans selected</t>
+          <t>User has opened comparison tool with multiple plans</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1. View comparison tool 2. Locate covered services section 3. Compare service coverage across plans</t>
+          <t>1. Open comparison tool 2. Locate estimated costs section 3. Review costs for common services 4. Compare across plans</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Covered services are listed for each plan; Coverage differences are highlighted; Services covered by some but not all plans are clearly marked; User can easily identify coverage gaps</t>
+          <t>Estimated costs shown for primary care visit, specialist visit, urgent care, generic prescription; Costs are clearly labeled as estimates; Differences are easy to compare; Disclaimer about estimates is displayed</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2536,27 +2536,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Verify comparison of estimated costs for common services</t>
+          <t>Verify comparison tool displays provider network breadth</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Validate that estimated costs for common healthcare services are compared</t>
+          <t>Validate that provider network information is compared</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>User has opened comparison tool with 2-3 plans selected</t>
+          <t>User has opened comparison tool with multiple plans</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1. View comparison tool 2. Locate estimated costs section 3. Review costs for common services (PCP visit, specialist, urgent care, generic Rx)</t>
+          <t>1. Open comparison tool 2. Locate provider network section 3. Review network breadth for each plan 4. Compare network sizes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Estimated costs are displayed for each common service; Costs are shown for each plan; Lowest cost option is highlighted; Disclaimer indicates these are estimates</t>
+          <t>Provider network breadth is indicated (e.g., number of providers, network type); User's selected providers' network status is shown; Differences in network access are clear; Network size comparison is meaningful</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2578,27 +2578,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Verify comparison of provider network breadth</t>
+          <t>Verify comparison tool displays prescription drug coverage</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Validate that provider network information is compared across plans</t>
+          <t>Validate that medication coverage is compared across plans</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>User has opened comparison tool with 2-3 plans selected</t>
+          <t>User has opened comparison tool and entered medications</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1. View comparison tool 2. Locate provider network section 3. Compare network breadth across plans</t>
+          <t>1. Open comparison tool 2. Locate prescription coverage section 3. Review medication coverage for each plan 4. Compare formulary tiers and costs</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Network breadth information is displayed (e.g., number of providers, network type); User's selected providers' status is shown for each plan; Network differences are highlighted; User can assess network adequacy</t>
+          <t>User's medications are listed with coverage status for each plan; Formulary tiers are shown; Estimated costs for each medication by plan are displayed; Differences are highlighted</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2620,27 +2620,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Verify comparison highlights differences between plans</t>
+          <t>Verify comparison tool highlighting of key differences</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Validate that key differences between plans are visually highlighted</t>
+          <t>Validate that significant differences between plans are visually highlighted</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>User has opened comparison tool with 2-3 plans selected</t>
+          <t>User has opened comparison tool with plans that have notable differences</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1. View comparison tool 2. Scan for visual highlighting 3. Identify key differences</t>
+          <t>1. Open comparison tool 2. Review entire comparison 3. Identify highlighted differences 4. Verify highlighting logic</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Differences between plans are visually highlighted (color coding, bold text, icons); Similar features are also indicated; User can quickly identify pros and cons of each plan; Visual design aids decision-making</t>
+          <t>Key differences are visually highlighted (color, bold, icons); Highlighting helps user quickly identify important variations; Most significant differences are emphasized; Highlighting is consistent and intuitive</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2662,27 +2662,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Verify comparison tool with only one plan selected</t>
+          <t>Verify comparison tool with attempt to compare more than three plans</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Validate system handling when user attempts comparison with single plan</t>
+          <t>Validate system behavior when user tries to compare more than three plans</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>User has selected only one plan</t>
+          <t>User has selected three plans for comparison</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1. Select one plan 2. Attempt to open comparison tool 3. Observe system response</t>
+          <t>1. Select three plans for comparison 2. Attempt to select fourth plan 3. Observe system response</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>System prompts user to select at least one more plan for comparison OR displays single plan details; User receives clear guidance; Comparison tool requires minimum 2 plans; Helpful message is displayed</t>
+          <t>System prevents selection of more than three plans; Clear message explains three-plan limit; User must deselect a plan before adding another; Limit is enforced consistently</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2704,27 +2704,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Verify comparison tool with more than three plans selected</t>
+          <t>Verify comparison tool with only one plan selected</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Validate system handling when user attempts to compare more than three plans</t>
+          <t>Validate system behavior when user tries to compare single plan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>User attempts to select 4 or more plans</t>
+          <t>User has selected only one plan</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1. Select first three plans 2. Attempt to select fourth plan 3. Observe system response</t>
+          <t>1. Select one plan 2. Attempt to open comparison tool 3. Observe system response</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>System limits selection to maximum 3 plans; User is informed of the limit; User must deselect a plan before selecting another; Clear message explains the limitation</t>
+          <t>System either prevents opening comparison tool or displays message that at least two plans are needed; User is prompted to select additional plans; Appropriate guidance is provided</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Edge</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -2746,27 +2746,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Verify comparison tool print functionality</t>
+          <t>Verify comparison tool export or print functionality</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Validate that users can print the plan comparison</t>
+          <t>Validate that users can export or print comparison results</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>User has opened comparison tool with 2-3 plans</t>
+          <t>User has opened comparison tool with multiple plans</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1. Open comparison tool 2. Locate print option 3. Click print 4. Review print preview</t>
+          <t>1. Open comparison tool with 2-3 plans 2. Locate export or print option 3. Select export to PDF or print 4. Review output</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Print option is available; Print preview shows comparison in readable format; All key information is included in print version; Print layout is optimized for paper</t>
+          <t>Comparison can be exported to PDF or printed; Output maintains formatting and readability; All comparison data is included; User can save for offline review</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2788,27 +2788,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Verify comparison tool export/save functionality</t>
+          <t>Verify comparison tool responsiveness on mobile device</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Validate that users can save or export the plan comparison</t>
+          <t>Validate that comparison tool is usable on mobile devices</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>User has opened comparison tool with 2-3 plans</t>
+          <t>User is accessing system on mobile device</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1. Open comparison tool 2. Locate save/export option 3. Save or export comparison 4. Verify saved content</t>
+          <t>1. Access comparison tool on smartphone 2. Select plans for comparison 3. Review comparison display 4. Test scrolling and interaction</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Save/export option is available; Comparison can be saved as PDF or other format; Saved version includes all comparison details; User can access saved comparison later</t>
+          <t>Comparison tool is responsive and usable on mobile; Information is readable without excessive zooming; User can scroll horizontally to view all plans; Touch interactions work properly</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2830,27 +2830,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Verify enrollment workflow completion time tracking</t>
+          <t>Verify enrollment workflow completion time under 15 minutes</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Validate that system tracks time from start to plan recommendation display</t>
+          <t>Validate that average user can complete workflow within time requirement</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>User begins enrollment workflow; Analytics tracking is enabled</t>
+          <t>New user starting enrollment process; Session analytics are enabled</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1. Start enrollment workflow and note time 2. Complete medication input 3. Complete provider selection 4. Complete financial preferences 5. View plan recommendations 6. Check elapsed time</t>
+          <t>1. Start enrollment workflow timer 2. Input medications (2-3 medications) 3. Search and select providers (1 PCP, 1 specialist) 4. Enter financial preferences 5. Review recommendations 6. Use comparison tool 7. Complete workflow 8. Record total time</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>System tracks session time; Time from start to plan recommendations is recorded; Analytics capture workflow duration; Timestamp data is available for analysis</t>
+          <t>Total time from start to viewing comparison is under 15 minutes for average user; Session analytics capture timing data; Workflow is streamlined and intuitive; No unnecessary delays or bottlenecks</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2872,27 +2872,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Verify average user can complete workflow in under 15 minutes</t>
+          <t>Verify enrollment workflow performance with maximum data input</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Validate that workflow is achievable within 15-minute target</t>
+          <t>Validate system performance when user enters maximum allowed data</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Average user with typical data (3-5 medications, 2-3 providers, standard preferences)</t>
+          <t>User is on enrollment workflow</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1. Start workflow timer 2. Enter 3-5 medications 3. Select 2-3 providers 4. Enter financial preferences 5. View plan recommendations 6. Verify total time</t>
+          <t>1. Enter maximum number of medications allowed 2. Select maximum number of providers allowed 3. Enter all financial preferences 4. Generate recommendations 5. Open comparison tool 6. Measure response times</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Workflow can be completed in under 15 minutes; User interface is intuitive and efficient; No unnecessary delays or steps; Performance meets AC6 requirement</t>
+          <t>System handles maximum data input without performance degradation; Response times remain acceptable; Recommendations generate within reasonable time; Comparison tool loads without delay</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Edge</t>
         </is>
       </c>
     </row>
@@ -2914,32 +2914,32 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Verify workflow performance with maximum data input</t>
+          <t>Verify enrollment workflow with minimal data input</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Validate system performance when user enters maximum allowed data</t>
+          <t>Validate that workflow can be completed with minimal required data</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>User enters maximum medications, multiple providers, detailed preferences</t>
+          <t>User is on enrollment workflow</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1. Start workflow 2. Enter maximum number of medications 3. Select multiple providers 4. Enter detailed financial preferences 5. Submit for recommendations 6. Measure response time</t>
+          <t>1. Skip optional medication input 2. Skip optional provider selection 3. Enter only required financial preferences 4. Generate recommendations 5. Review results</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>System handles maximum data input efficiently; Response time remains acceptable; Plan recommendations are generated without timeout; System remains responsive throughout</t>
+          <t>System generates recommendations with minimal input; Required vs optional fields are clear; Recommendations are still relevant; User can complete workflow quickly</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2956,37 +2956,37 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Verify HIPAA compliance for medication data storage</t>
+          <t>Verify session timeout handling during enrollment</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Validate that medication information is stored in compliance with HIPAA</t>
+          <t>Validate system behavior when user session times out during enrollment</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>User has entered medication information; Data storage mechanisms are in place</t>
+          <t>User is in middle of enrollment workflow</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1. Enter medication data 2. Submit data 3. Verify data is stored 4. Check encryption at rest 5. Review access controls</t>
+          <t>1. Begin enrollment workflow 2. Enter some data 3. Leave session idle beyond timeout period 4. Attempt to continue 5. Observe system behavior</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Medication data is encrypted at rest; Access is restricted to authorized users only; Audit logs track data access; Storage complies with HIPAA Security Rule</t>
+          <t>System displays session timeout message; User is prompted to log in again; Previously entered data is either saved or user is warned of data loss; Security is maintained</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Edge</t>
         </is>
       </c>
     </row>
@@ -2998,32 +2998,32 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Verify HIPAA compliance for provider preference data storage</t>
+          <t>Verify data persistence when user navigates away</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Validate that provider selection data is stored in compliance with HIPAA</t>
+          <t>Validate that entered data is saved when user navigates to different page</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>User has selected providers; Data storage mechanisms are in place</t>
+          <t>User has entered data in enrollment workflow</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1. Select providers 2. Submit data 3. Verify data is stored 4. Check encryption at rest 5. Review access controls</t>
+          <t>1. Enter medications and providers 2. Navigate to different page or section 3. Return to enrollment workflow 4. Verify data persistence</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Provider preference data is encrypted at rest; Access is restricted to authorized users only; Audit logs track data access; Storage complies with HIPAA Security Rule</t>
+          <t>Previously entered data is retained; User does not need to re-enter information; Data persists across navigation; User experience is seamless</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3040,27 +3040,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Verify HIPAA compliance for demographic data storage</t>
+          <t>Verify HIPAA compliance for medication data storage</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Validate that demographic information is stored in compliance with HIPAA</t>
+          <t>Validate that medication information is stored in compliance with HIPAA</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>User has entered demographic information; Data storage mechanisms are in place</t>
+          <t>User has entered medication data</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1. Enter demographic data 2. Submit data 3. Verify data is stored 4. Check encryption at rest 5. Review access controls</t>
+          <t>1. Enter medication information 2. Submit data 3. Verify data storage method 4. Check encryption at rest 5. Review access logs</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Demographic data is encrypted at rest; Access is restricted to authorized users only; Audit logs track data access; Storage complies with HIPAA Privacy Rule</t>
+          <t>Medication data is encrypted at rest using HIPAA-compliant encryption (AES-256 or equivalent); Access is logged and auditable; Data is stored in secure database; Compliance requirements are met</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3082,27 +3082,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Verify encryption in transit for all health data</t>
+          <t>Verify HIPAA compliance for provider preference data storage</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Validate that all health information is encrypted during transmission</t>
+          <t>Validate that provider selection data is stored securely</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>User is entering health information; Network monitoring tools are available</t>
+          <t>User has selected providers</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1. Enter medication data 2. Submit data 3. Monitor network traffic 4. Verify encryption protocol (TLS 1.2 or higher) 5. Repeat for provider and demographic data</t>
+          <t>1. Select preferred providers 2. Submit data 3. Verify data storage method 4. Check encryption at rest 5. Review access controls</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>All health data transmission uses TLS 1.2 or higher; No unencrypted health data is transmitted; Secure protocols are enforced; Encryption in transit meets HIPAA requirements</t>
+          <t>Provider preference data is encrypted at rest; Access controls limit who can view data; Storage complies with HIPAA Security Rule; Audit trails are maintained</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3124,27 +3124,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Verify encryption at rest for all health data</t>
+          <t>Verify HIPAA compliance for data transmission encryption</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Validate that all stored health information is encrypted</t>
+          <t>Validate that all health data is encrypted in transit</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Health data has been stored in database; Database encryption is configured</t>
+          <t>User is submitting health information</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1. Store health data 2. Access database directly 3. Verify data is encrypted 4. Check encryption algorithm (AES-256 or equivalent) 5. Verify encryption keys are managed securely</t>
+          <t>1. Enter health data (medications, conditions) 2. Submit data to server 3. Monitor network traffic 4. Verify encryption protocol</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>All health data is encrypted at rest using strong encryption (AES-256 or equivalent); Encryption keys are securely managed; Data is unreadable without proper decryption; Encryption at rest meets HIPAA requirements</t>
+          <t>All data transmission uses TLS 1.2 or higher; Health information is encrypted in transit; No plain text transmission of PHI; Encryption meets HIPAA requirements</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3166,27 +3166,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Verify audit logging for health data access</t>
+          <t>Verify HIPAA compliance for demographic data storage</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Validate that all access to health information is logged</t>
+          <t>Validate that demographic information is stored securely</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>User accesses health data; Audit logging is enabled</t>
+          <t>User has entered demographic data</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1. Access medication data 2. Access provider data 3. Access demographic data 4. Review audit logs 5. Verify log completeness</t>
+          <t>1. Enter demographic information 2. Submit data 3. Verify storage security 4. Check encryption and access controls</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>All health data access is logged; Logs include user ID, timestamp, data accessed, and action performed; Logs are tamper-proof; Audit trail meets HIPAA requirements</t>
+          <t>Demographic data is encrypted at rest; Access is restricted to authorized personnel only; Data storage complies with HIPAA Privacy Rule; Audit logs track all access</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3208,27 +3208,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Verify role-based access control for health data</t>
+          <t>Verify secure handling of chronic condition information</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Validate that access to health information is restricted based on user roles</t>
+          <t>Validate that chronic condition data is protected as PHI</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Multiple user roles exist; RBAC is configured</t>
+          <t>User is entering chronic condition information</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1. Login as user with limited role 2. Attempt to access health data 3. Verify access restrictions 4. Login as authorized role 5. Verify appropriate access</t>
+          <t>1. Enter chronic condition data 2. Submit information 3. Verify security measures 4. Check encryption and access logs</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Access to health data is restricted by role; Unauthorized roles cannot access protected data; Authorized roles have appropriate access levels; RBAC meets HIPAA requirements</t>
+          <t>Chronic condition data is treated as PHI; Encryption at rest and in transit is enforced; Access is logged and restricted; HIPAA compliance is maintained</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -3250,27 +3250,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Verify session timeout for inactive users</t>
+          <t>Verify audit logging for health data access</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Validate that user sessions timeout after period of inactivity</t>
+          <t>Validate that all access to health information is logged</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>User is logged in; Session timeout is configured</t>
+          <t>System administrator or authorized user accesses health data</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1. Login to system 2. Enter some data 3. Remain inactive for configured timeout period 4. Attempt to continue workflow</t>
+          <t>1. Access user's health information 2. View medications and conditions 3. Check audit logs 4. Verify log completeness</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Session times out after configured period (e.g., 15 minutes); User is logged out automatically; Unsaved data handling is appropriate; User must re-authenticate to continue</t>
+          <t>All access to PHI is logged with timestamp, user ID, and action; Logs are tamper-proof and retained per HIPAA requirements; Unauthorized access attempts are logged; Logs are reviewable for compliance audits</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -3292,27 +3292,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Verify secure password requirements</t>
+          <t>Verify role-based access control for health data</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Validate that system enforces strong password requirements</t>
+          <t>Validate that only authorized roles can access health information</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>User is creating account or changing password</t>
+          <t>Different user roles attempt to access health data</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1. Attempt to set weak password (e.g., 12345) 2. Observe rejection 3. Attempt password without special characters 4. Observe rejection 5. Set strong password meeting all requirements</t>
+          <t>1. Log in as unauthorized role 2. Attempt to access health data 3. Verify access denial 4. Log in as authorized role 5. Verify access granted</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>System enforces password complexity requirements; Minimum length is enforced (e.g., 8+ characters); Mix of uppercase, lowercase, numbers, and special characters required; Weak passwords are rejected with clear guidance</t>
+          <t>Unauthorized roles cannot access PHI; Authorized roles have appropriate access levels; Access control is enforced consistently; Role permissions align with HIPAA minimum necessary standard</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -3334,32 +3334,32 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Verify display of estimated OOP costs for primary care visit</t>
+          <t>Verify data retention policy compliance</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Validate that estimated cost for primary care visit is displayed for each plan</t>
+          <t>Validate that health data retention follows HIPAA and business requirements</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>User is viewing plan recommendations or comparison; Cost estimation data is available</t>
+          <t>Health data has been stored for specified period</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1. View plan details or comparison 2. Locate estimated costs section 3. Find primary care visit cost 4. Verify cost is displayed for each plan</t>
+          <t>1. Review data retention policy 2. Check stored health data age 3. Verify retention periods 4. Confirm secure disposal process</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Estimated cost for primary care visit is displayed; Cost is shown for each recommended plan; Disclaimer indicates estimate based on plan benefits and historical averages; Cost differences across plans are clear</t>
+          <t>Data is retained for required period (typically 6 years minimum); Expired data is securely disposed; Retention policy is documented and followed; Compliance with HIPAA and state laws is maintained</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3376,27 +3376,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Verify display of estimated OOP costs for specialist visit</t>
+          <t>Verify estimated cost display for primary care visit</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Validate that estimated cost for specialist visit is displayed for each plan</t>
+          <t>Validate that estimated cost for primary care visit is shown for each plan</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>User is viewing plan recommendations or comparison; Cost estimation data is available</t>
+          <t>User is viewing plan recommendations or comparison</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1. View plan details or comparison 2. Locate estimated costs section 3. Find specialist visit cost 4. Verify cost is displayed for each plan</t>
+          <t>1. View plan details or comparison 2. Locate estimated costs section 3. Find primary care visit cost 4. Verify display for each plan</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Estimated cost for specialist visit is displayed; Cost is shown for each recommended plan; Disclaimer indicates estimate based on plan benefits and historical averages; Cost differences across plans are clear</t>
+          <t>Estimated cost for primary care visit is displayed for each plan; Cost includes copay or coinsurance; Disclaimer indicates estimate based on plan benefits; Differences across plans are clear</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -3418,27 +3418,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Verify display of estimated OOP costs for urgent care</t>
+          <t>Verify estimated cost display for specialist visit</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Validate that estimated cost for urgent care visit is displayed for each plan</t>
+          <t>Validate that estimated cost for specialist visit is shown for each plan</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>User is viewing plan recommendations or comparison; Cost estimation data is available</t>
+          <t>User is viewing plan recommendations or comparison</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1. View plan details or comparison 2. Locate estimated costs section 3. Find urgent care visit cost 4. Verify cost is displayed for each plan</t>
+          <t>1. View plan details or comparison 2. Locate estimated costs section 3. Find specialist visit cost 4. Verify display for each plan</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Estimated cost for urgent care visit is displayed; Cost is shown for each recommended plan; Disclaimer indicates estimate based on plan benefits and historical averages; Cost differences across plans are clear</t>
+          <t>Estimated cost for specialist visit is displayed for each plan; Cost reflects plan's specialist copay or coinsurance; Estimate disclaimer is present; User can compare specialist costs across plans</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -3460,27 +3460,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Verify display of estimated OOP costs for generic prescription refill</t>
+          <t>Verify estimated cost display for urgent care visit</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Validate that estimated cost for generic prescription refill is displayed for each plan</t>
+          <t>Validate that estimated cost for urgent care is shown for each plan</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>User is viewing plan recommendations or comparison; Cost estimation data is available</t>
+          <t>User is viewing plan recommendations or comparison</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1. View plan details or comparison 2. Locate estimated costs section 3. Find generic prescription refill cost 4. Verify cost is displayed for each plan</t>
+          <t>1. View plan details or comparison 2. Locate estimated costs section 3. Find urgent care visit cost 4. Verify display for each plan</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Estimated cost for generic prescription refill is displayed; Cost is shown for each recommended plan; Disclaimer indicates estimate based on plan benefits and historical averages; Cost differences across plans are clear</t>
+          <t>Estimated cost for urgent care visit is displayed for each plan; Cost reflects plan's urgent care copay; Estimate is clearly labeled; Comparison across plans is easy</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -3502,27 +3502,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Verify disclaimer for estimated costs</t>
+          <t>Verify estimated cost display for generic prescription refill</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Validate that appropriate disclaimer is displayed with estimated costs</t>
+          <t>Validate that estimated cost for generic prescription is shown for each plan</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>User is viewing estimated costs for any service</t>
+          <t>User is viewing plan recommendations or comparison</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1. Navigate to estimated costs section 2. Locate disclaimer text 3. Read disclaimer content</t>
+          <t>1. View plan details or comparison 2. Locate estimated costs section 3. Find generic prescription refill cost 4. Verify display for each plan</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Disclaimer clearly states costs are estimates; Disclaimer indicates estimates based on plan benefits and historical averages; Disclaimer notes actual costs may vary; Disclaimer is prominently displayed and readable</t>
+          <t>Estimated cost for generic prescription refill is displayed; Cost reflects Tier 1 formulary pricing; 30-day or 90-day supply may be specified; Estimate disclaimer is present</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -3544,27 +3544,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Verify estimated costs reflect user's specific medications</t>
+          <t>Verify estimated cost disclaimer is displayed</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Validate that cost estimates consider user's actual medication list</t>
+          <t>Validate that clear disclaimer about cost estimates is shown</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>User has entered specific medications; Cost estimates are displayed</t>
+          <t>User is viewing estimated costs</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1. Enter specific medications 2. View plan recommendations 3. Check estimated prescription costs 4. Verify costs reflect entered medications</t>
+          <t>1. Navigate to estimated costs section 2. Review cost estimates 3. Locate disclaimer text 4. Verify disclaimer content</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Estimated prescription costs are based on user's actual medications; Costs reflect formulary tier of user's medications; Estimates are personalized to user's needs; Generic vs. brand costs are accurately reflected</t>
+          <t>Disclaimer clearly states costs are estimates; Explanation that estimates are based on plan benefits and historical averages; User is informed actual costs may vary; Disclaimer is prominently displayed</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3586,27 +3586,27 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Verify estimated costs calculation using historical claims data</t>
+          <t>Verify estimated cost calculation based on historical data</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Validate that cost estimates leverage historical claims data</t>
+          <t>Validate that cost estimates use historical claims data</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Cost estimation engine is configured; Historical claims data is available</t>
+          <t>System is generating cost estimates</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1. View estimated costs for services 2. Verify calculation methodology 3. Confirm historical data is used</t>
+          <t>1. Review cost estimation methodology 2. Verify use of historical claims data 3. Check calculation logic 4. Validate estimate accuracy</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Cost estimates are calculated using historical claims data; Averages are based on actual claim history; Estimates reflect typical costs for services; Calculation methodology is sound and documented</t>
+          <t>Cost estimates incorporate historical claims data; Calculations use statistical averages; Methodology is documented; Estimates are reasonable and defensible</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3628,27 +3628,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Verify cost estimates for user with chronic conditions</t>
+          <t>Verify estimated out-of-pocket cost for common services</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Validate that cost estimates account for chronic condition management</t>
+          <t>Validate that out-of-pocket costs are estimated for multiple common services</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>User has indicated chronic conditions; Cost estimation considers chronic care</t>
+          <t>User is viewing plan details</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1. Enter chronic condition information 2. View plan recommendations 3. Review estimated costs 4. Verify costs reflect chronic care needs</t>
+          <t>1. View plan recommendations 2. Locate out-of-pocket cost estimates 3. Review estimates for multiple service types 4. Verify comprehensiveness</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Cost estimates include chronic condition management; Estimates account for regular specialist visits, medications, and monitoring; Plans are compared based on total cost of chronic care; User can make informed decision for chronic condition management</t>
+          <t>Out-of-pocket costs estimated for primary care, specialist, urgent care, ER, generic Rx, and other common services; Estimates account for deductible and coinsurance; Total estimated annual out-of-pocket may be shown; Information helps user make informed decision</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3670,27 +3670,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Verify responsive design on desktop browser</t>
+          <t>Verify cost estimate updates when plan selection changes</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Validate that enrollment workflow displays correctly on desktop browsers</t>
+          <t>Validate that cost estimates update dynamically when user changes plan selection</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>User accesses system via desktop browser (Chrome, Firefox, Edge, Safari)</t>
+          <t>User is comparing multiple plans</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1. Open enrollment workflow in desktop browser 2. Navigate through all sections 3. Verify layout and functionality 4. Test on multiple browsers</t>
+          <t>1. View cost estimates for Plan A 2. Switch to Plan B 3. Observe cost estimate updates 4. Verify accuracy</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Workflow displays correctly on desktop; All features are accessible and functional; Layout is optimized for desktop screen sizes; Consistent experience across major browsers</t>
+          <t>Cost estimates update immediately when plan changes; Estimates reflect selected plan's benefits; No stale data is displayed; Updates occur without page reload</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3712,27 +3712,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Verify responsive design on tablet device</t>
+          <t>Verify accessibility compliance for enrollment workflow</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Validate that enrollment workflow displays correctly on tablet devices</t>
+          <t>Validate that enrollment workflow meets WCAG 2.1 AA accessibility standards</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>User accesses system via tablet (iPad, Android tablet)</t>
+          <t>User with assistive technology is accessing enrollment workflow</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1. Open enrollment workflow on tablet 2. Navigate through all sections 3. Verify layout and functionality 4. Test touch interactions</t>
+          <t>1. Navigate enrollment workflow using screen reader 2. Test keyboard-only navigation 3. Verify color contrast ratios 4. Check form labels and ARIA attributes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Workflow displays correctly on tablet; Layout adapts to tablet screen size; Touch interactions work properly; All features remain accessible</t>
+          <t>All form fields have proper labels; Keyboard navigation works throughout workflow; Color contrast meets WCAG standards; Screen reader announces all relevant information; Accessibility compliance is maintained</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3754,27 +3754,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Verify responsive design on mobile device</t>
+          <t>Verify error handling for database connection failure</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Validate that enrollment workflow displays correctly on mobile phones</t>
+          <t>Validate system behavior when database connection is lost</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>User accesses system via mobile phone (iOS, Android)</t>
+          <t>System is operational; Database connection is interrupted</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1. Open enrollment workflow on mobile phone 2. Navigate through all sections 3. Verify layout and functionality 4. Test touch interactions</t>
+          <t>1. Begin enrollment workflow 2. Simulate database connection failure 3. Attempt to submit data 4. Observe error handling</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Workflow displays correctly on mobile; Layout adapts to small screen size; Touch interactions work properly; All features remain accessible; Mobile-optimized navigation is provided</t>
+          <t>System displays user-friendly error message; User is informed of technical issue; Data is not lost if possible; User can retry or contact support; Error is logged for technical team</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -3796,37 +3796,37 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Verify accessibility compliance for screen readers</t>
+          <t>Verify error handling for formulary service unavailability</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Validate that enrollment workflow is accessible to screen reader users</t>
+          <t>Validate system behavior when formulary validation service is unavailable</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>User with screen reader software accesses system</t>
+          <t>User is entering medications; Formulary service is down</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1. Navigate workflow using screen reader 2. Verify all content is readable 3. Test form field labels 4. Verify button and link descriptions</t>
+          <t>1. Enter medication name 2. Attempt to validate against formulary 3. Observe system response</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>All content is accessible to screen readers; Form fields have proper labels; Buttons and links have descriptive text; ARIA labels are properly implemented; Workflow meets WCAG 2.1 AA standards</t>
+          <t>System displays message that formulary validation is temporarily unavailable; User can still enter medications; Validation may occur later; User experience is gracefully degraded</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -3838,37 +3838,37 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Verify keyboard navigation support</t>
+          <t>Verify error handling for provider directory service unavailability</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Validate that entire workflow can be navigated using keyboard only</t>
+          <t>Validate system behavior when provider directory is unavailable</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>User navigates system using keyboard only (no mouse)</t>
+          <t>User is searching for providers; Provider service is down</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1. Navigate workflow using Tab key 2. Activate buttons using Enter/Space 3. Complete entire workflow without mouse 4. Verify focus indicators</t>
+          <t>1. Attempt to search for provider 2. Observe system response 3. Check error messaging</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>All interactive elements are keyboard accessible; Tab order is logical; Focus indicators are visible; Workflow can be completed entirely with keyboard; Meets accessibility standards</t>
+          <t>System displays message that provider search is temporarily unavailable; User is provided alternative (phone number, try later); Enrollment can continue without provider selection; Error is handled gracefully</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -3880,37 +3880,37 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Verify color contrast for readability</t>
+          <t>Verify concurrent user session handling</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Validate that color contrast meets accessibility standards</t>
+          <t>Validate system behavior when user has multiple active sessions</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>User with visual impairment or color blindness accesses system</t>
+          <t>User logs in from two different devices simultaneously</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1. Review all text and background color combinations 2. Test with color contrast analyzer 3. Verify contrast ratios 4. Test with color blindness simulators</t>
+          <t>1. Log in from first device 2. Begin enrollment workflow 3. Log in from second device 4. Continue enrollment on both 5. Observe behavior</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>All text meets minimum contrast ratio (4.5:1 for normal text, 3:1 for large text); Information is not conveyed by color alone; Color choices accommodate color blindness; Meets WCAG 2.1 AA standards</t>
+          <t>System either allows concurrent sessions with data sync or restricts to single session; User is notified of multiple sessions if restricted; Data consistency is maintained; Security is not compromised</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Edge</t>
         </is>
       </c>
     </row>
@@ -3922,32 +3922,32 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Verify form validation error messages are clear and helpful</t>
+          <t>Verify browser back button handling during enrollment</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Validate that validation errors provide clear guidance to users</t>
+          <t>Validate that browser back button works correctly during enrollment workflow</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>User enters invalid data in various fields</t>
+          <t>User is in middle of enrollment workflow</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1. Enter invalid data in medication field 2. Review error message 3. Enter invalid data in financial fields 4. Review error messages 5. Test multiple validation scenarios</t>
+          <t>1. Complete first step of enrollment 2. Move to second step 3. Click browser back button 4. Verify data persistence and navigation</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Error messages are clear and specific; Messages explain what is wrong and how to fix it; Errors are displayed near relevant fields; Error styling is consistent; Users can easily correct errors</t>
+          <t>Browser back button navigates to previous step; Previously entered data is retained; User can move forward again without re-entering data; Navigation is intuitive</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Usability</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3964,32 +3964,32 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Verify progress indicator throughout workflow</t>
+          <t>Verify form auto-save functionality</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Validate that users can see their progress through the enrollment workflow</t>
+          <t>Validate that enrollment form data is automatically saved</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>User is navigating through enrollment workflow</t>
+          <t>User is entering data in enrollment workflow</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1. Start enrollment workflow 2. Complete first section 3. Observe progress indicator 4. Continue through workflow 5. Verify progress updates</t>
+          <t>1. Enter data in enrollment form 2. Wait for auto-save interval 3. Verify data is saved 4. Refresh page or navigate away and return</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Progress indicator is visible throughout workflow; Indicator shows current step and total steps; User can see how much remains; Progress updates as user advances; User can navigate to previous steps if needed</t>
+          <t>Form data is automatically saved at regular intervals; User sees confirmation of auto-save; Data persists after page refresh; User does not lose work</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Usability</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4006,27 +4006,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Verify ability to save and resume enrollment later</t>
+          <t>Verify plan recommendation refresh after criteria change</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Validate that users can save progress and return to complete enrollment later</t>
+          <t>Validate that plan recommendations update when user modifies input criteria</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>User begins enrollment but cannot complete in one session</t>
+          <t>User has received initial plan recommendations</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1. Start enrollment workflow 2. Complete some sections 3. Save progress 4. Logout or close browser 5. Return later and resume</t>
+          <t>1. View initial plan recommendations 2. Modify medication list 3. Request updated recommendations 4. Verify recommendations change appropriately</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>User can save progress at any point; Saved data is retained securely; User can resume from where they left off; All entered data is preserved; Session can be resumed within reasonable timeframe</t>
+          <t>Plan recommendations refresh based on updated criteria; New recommendations reflect changes in medications, providers, or financial preferences; User can easily update and refresh; System recalculates recommendations accurately</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -4048,32 +4048,32 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Verify help and guidance throughout workflow</t>
+          <t>Verify handling of plan with limited provider network</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Validate that contextual help is available to assist users</t>
+          <t>Validate system behavior when recommended plan has very limited provider network</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>User needs assistance during enrollment</t>
+          <t>User is viewing plan recommendations; One plan has minimal provider network</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>1. Navigate to various sections 2. Look for help icons or links 3. Access help content 4. Verify relevance and clarity</t>
+          <t>1. View plan recommendations 2. Select plan with limited network 3. Review provider network information 4. Check for warnings or notifications</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Help icons or links are available throughout workflow; Help content is contextual and relevant; Tooltips explain complex terms; FAQs or guided help is accessible; Users can get assistance without leaving workflow</t>
+          <t>System clearly indicates limited provider network; Warning or notification alerts user; Network size comparison with other plans is shown; User can make informed decision</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Usability</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4090,32 +4090,32 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Verify glossary for health insurance terms</t>
+          <t>Verify handling of plan with high deductible</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Validate that definitions are available for health insurance terminology</t>
+          <t>Validate that high deductible plans are clearly identified</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>User encounters unfamiliar health insurance terms</t>
+          <t>User is viewing plan recommendations; High deductible plans are available</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>1. Locate terms like deductible, co-pay, formulary, etc. 2. Access term definitions 3. Verify clarity of definitions</t>
+          <t>1. View plan recommendations 2. Identify high deductible health plans (HDHP) 3. Review deductible information 4. Check for HDHP designation</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Glossary or definitions are available for key terms; Terms are explained in plain language; Definitions are accessible via tooltips or links; Users can understand health insurance concepts</t>
+          <t>High deductible plans are clearly labeled; HDHP designation is shown if applicable; HSA eligibility is indicated; User understands implications of high deductible</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Usability</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4132,32 +4132,32 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Verify plan selection and enrollment submission</t>
+          <t>Verify integration with external formulary database</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Validate that user can select a plan and submit enrollment</t>
+          <t>Validate that system correctly integrates with external formulary data source</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>User has reviewed plan recommendations and made decision</t>
+          <t>System is configured to use external formulary database</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>1. Select preferred plan 2. Review plan details 3. Confirm selection 4. Submit enrollment 5. Verify submission</t>
+          <t>1. Enter medication name 2. System queries external formulary database 3. Receive and display formulary information 4. Verify data accuracy</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>User can select a plan from recommendations; Confirmation step prevents accidental submission; Enrollment is submitted successfully; User receives confirmation of submission; Confirmation includes plan details and next steps</t>
+          <t>System successfully queries external formulary database; Data is retrieved and displayed correctly; Response time is acceptable; Integration is reliable and error-handled</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Verify enrollment confirmation display</t>
+          <t>Verify integration with provider directory system</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Validate that user receives clear confirmation after enrollment submission</t>
+          <t>Validate that system correctly integrates with provider directory</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>User has submitted enrollment</t>
+          <t>System is configured to use provider directory service</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>1. Submit enrollment 2. View confirmation page 3. Review confirmation details</t>
+          <t>1. Search for provider 2. System queries provider directory 3. Receive and display provider information 4. Verify data accuracy and currency</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Confirmation page is displayed; Confirmation includes plan name and key details; Enrollment ID or reference number is provided; Next steps are clearly explained; User can print or save confirmation</t>
+          <t>System successfully queries provider directory; Provider information is current and accurate; Network status is validated in real-time; Integration is reliable</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4216,27 +4216,27 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Verify enrollment confirmation email</t>
+          <t>Verify cross-browser compatibility for enrollment workflow</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Validate that user receives confirmation email after enrollment</t>
+          <t>Validate that enrollment workflow functions correctly across major browsers</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>User has submitted enrollment; Email system is configured</t>
+          <t>User accesses system from different browsers</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>1. Submit enrollment 2. Check email inbox 3. Verify confirmation email received 4. Review email content</t>
+          <t>1. Access enrollment workflow in Chrome 2. Complete workflow and verify functionality 3. Repeat in Firefox 4. Repeat in Safari 5. Repeat in Edge</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Confirmation email is sent to user; Email includes plan details and enrollment information; Email includes reference number; Email provides contact information for questions; Email is received within reasonable timeframe</t>
+          <t>Enrollment workflow functions correctly in all major browsers; Display and formatting are consistent; All features work as expected; No browser-specific issues occur</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -4258,32 +4258,32 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Verify system performance under normal load</t>
+          <t>Verify mobile responsiveness of enrollment workflow</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Validate that system performs adequately under expected user load</t>
+          <t>Validate that enrollment workflow is fully functional on mobile devices</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>System is under normal operating load; Performance monitoring is active</t>
+          <t>User accesses system from mobile device</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>1. Access enrollment workflow during normal usage 2. Complete workflow 3. Measure response times 4. Monitor system resources</t>
+          <t>1. Access enrollment workflow on smartphone 2. Complete all steps of enrollment 3. Test all interactive elements 4. Verify display and usability</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Page load times are acceptable (under 3 seconds); Form submissions process quickly; Plan recommendations generate within 5 seconds; System remains responsive; No performance degradation</t>
+          <t>Enrollment workflow is fully responsive on mobile; All form fields are accessible and usable; Touch interactions work properly; User can complete entire workflow on mobile device</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4300,37 +4300,37 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Verify system performance under peak load</t>
+          <t>Verify tablet responsiveness of enrollment workflow</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Validate that system handles peak usage periods</t>
+          <t>Validate that enrollment workflow is optimized for tablet devices</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>System is under peak load (e.g., open enrollment period); Load testing tools are available</t>
+          <t>User accesses system from tablet device</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>1. Simulate peak user load 2. Access enrollment workflow 3. Complete workflow 4. Measure response times 5. Monitor system resources</t>
+          <t>1. Access enrollment workflow on tablet 2. Complete enrollment steps 3. Test comparison tool on tablet 4. Verify layout and usability</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>System handles peak load without failure; Response times remain acceptable; No users experience timeouts; System scales appropriately; Performance meets SLA requirements</t>
+          <t>Enrollment workflow is optimized for tablet screen size; Layout adapts appropriately; All features are accessible; User experience is positive on tablet</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Edge</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -4342,37 +4342,37 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Verify database connection failure handling</t>
+          <t>Verify plan enrollment confirmation</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Validate that system handles database connection failures gracefully</t>
+          <t>Validate that user receives confirmation after selecting a plan</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Database connection can be interrupted for testing</t>
+          <t>User has completed comparison and selected a plan</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>1. Start enrollment workflow 2. Simulate database connection failure 3. Attempt to submit data 4. Observe system behavior</t>
+          <t>1. Complete enrollment workflow 2. Select preferred plan 3. Confirm selection 4. Submit enrollment</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>System detects database connection failure; User receives appropriate error message; User data is not lost; System attempts to reconnect or provides retry option; Graceful degradation occurs</t>
+          <t>System displays enrollment confirmation; Confirmation includes plan details and effective date; Confirmation number is provided; User receives confirmation email</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Reliability</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -4384,37 +4384,37 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Verify external service failure handling (formulary validation)</t>
+          <t>Verify ability to save progress and return later</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Validate that system handles formulary service failures gracefully</t>
+          <t>Validate that users can save enrollment progress and complete later</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Formulary validation service can be made unavailable for testing</t>
+          <t>User is in middle of enrollment workflow</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>1. Enter medication 2. Simulate formulary service failure 3. Attempt to validate medication 4. Observe system behavior</t>
+          <t>1. Begin enrollment workflow 2. Enter partial information 3. Select Save and Exit option 4. Log out 5. Log back in later 6. Resume enrollment</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>System detects service failure; User receives appropriate error message; User can continue with workflow or retry; System provides fallback option if available; Error is logged for support team</t>
+          <t>User can save progress at any point; Saved data is retained; User can resume from where they left off; Save and resume functionality works reliably</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Reliability</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -4426,37 +4426,37 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Verify external service failure handling (provider network)</t>
+          <t>Verify handling of special enrollment period validation</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Validate that system handles provider network service failures gracefully</t>
+          <t>Validate that system verifies user eligibility for special enrollment period</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Provider network service can be made unavailable for testing</t>
+          <t>User is enrolling outside open enrollment period</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>1. Search for provider 2. Simulate provider service failure 3. Observe system behavior</t>
+          <t>1. Attempt to enroll outside open enrollment 2. System checks for special enrollment period eligibility 3. User provides qualifying event documentation 4. System validates eligibility</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>System detects service failure; User receives appropriate error message; User can retry or continue with workflow; System provides fallback option if available; Error is logged for support team</t>
+          <t>System validates special enrollment period eligibility; User is prompted for qualifying event; Documentation requirements are clear; Enrollment proceeds only if eligible</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Reliability</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -4468,37 +4468,37 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Verify data integrity during concurrent user sessions</t>
+          <t>Verify dependent enrollment functionality</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Validate that data integrity is maintained when same user has multiple sessions</t>
+          <t>Validate that users can enroll dependents during enrollment workflow</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>User can open multiple browser sessions</t>
+          <t>User is enrolling and has dependents to add</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>1. Login in first browser session 2. Login in second browser session 3. Enter different data in each session 4. Submit from both sessions 5. Verify data integrity</t>
+          <t>1. Begin enrollment workflow 2. Navigate to dependent section 3. Add dependent information 4. Select coverage for dependents 5. Review family plan options</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>System handles concurrent sessions appropriately; Data conflicts are detected and resolved; User is notified of concurrent session if applicable; Data integrity is maintained; No data corruption occurs</t>
+          <t>User can add multiple dependents; Dependent information is captured securely; Family plan options are displayed; Premium adjusts based on number of dependents</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Reliability</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Edge</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -4510,32 +4510,32 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Verify browser back button handling</t>
+          <t>Verify plan effective date display</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Validate that browser back button works correctly during enrollment</t>
+          <t>Validate that plan effective date is clearly communicated</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>User is in middle of enrollment workflow</t>
+          <t>User is reviewing plan selection</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>1. Complete first section 2. Move to second section 3. Click browser back button 4. Verify behavior 5. Continue workflow</t>
+          <t>1. Select a plan 2. Review plan details 3. Locate effective date information 4. Verify date accuracy</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Browser back button works as expected; User can navigate back to previous sections; Entered data is preserved; No errors occur; User can continue workflow normally</t>
+          <t>Plan effective date is clearly displayed; Date follows enrollment rules (e.g., first of next month); User understands when coverage begins; Effective date is accurate</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Usability</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4552,37 +4552,37 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Verify browser refresh handling</t>
+          <t>Verify premium payment method selection</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Validate that page refresh does not cause data loss</t>
+          <t>Validate that users can select payment method for premium</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>User is entering data in enrollment workflow</t>
+          <t>User has selected a plan and is completing enrollment</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>1. Enter data in form fields 2. Refresh browser page 3. Verify data preservation</t>
+          <t>1. Select preferred plan 2. Navigate to payment section 3. Choose payment method (bank account, credit card, payroll deduction) 4. Enter payment details</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Data is preserved after refresh OR user is warned before refresh; No unexpected data loss occurs; User can continue from current state; Session remains valid</t>
+          <t>User can select from available payment methods; Payment information is captured securely; Payment method is validated; PCI compliance is maintained for card data</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Usability</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Edge</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -4594,27 +4594,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Verify plan recommendation algorithm with edge case: all medications not covered</t>
+          <t>Verify handling of network timeout during enrollment</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Validate system behavior when no plan covers all user medications</t>
+          <t>Validate system behavior when network timeout occurs</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>User enters medications that are not covered by any single plan</t>
+          <t>User is submitting enrollment data; Network experiences timeout</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>1. Enter medications with limited coverage 2. Submit for recommendations 3. Review recommendations</t>
+          <t>1. Complete enrollment form 2. Submit data 3. Simulate network timeout 4. Observe system behavior</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>System still provides plan recommendations; Coverage gaps are clearly indicated; Plans with best partial coverage are shown; User is informed of coverage limitations; Alternative medication suggestions may be provided</t>
+          <t>System displays timeout error message; User is informed to retry; Data is preserved if possible; User does not lose entered information; Retry mechanism is available</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -4624,7 +4624,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Edge</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -4636,27 +4636,27 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Verify plan recommendation algorithm with edge case: all providers out of network</t>
+          <t>Verify plan comparison export includes all relevant data</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Validate system behavior when user's providers are not in any plan network</t>
+          <t>Validate that exported comparison contains complete information</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>User selects providers not in any available plan network</t>
+          <t>User has opened comparison tool and is exporting data</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>1. Select out-of-network providers 2. Submit for recommendations 3. Review recommendations</t>
+          <t>1. Select 2-3 plans for comparison 2. Open comparison tool 3. Export comparison to PDF 4. Review exported document</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>System still provides plan recommendations; Out-of-network status is clearly indicated; Plans with best out-of-network benefits are prioritized; User is informed of network limitations; Alternative provider suggestions may be provided</t>
+          <t>Exported document includes all comparison data; Formatting is preserved and readable; All plans are included; Document is suitable for offline review and decision-making</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -4666,847 +4666,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Edge</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>TC_ENR_101</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Verify plan recommendation algorithm with edge case: conflicting financial preferences</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Validate system behavior when financial preferences are unrealistic</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>User enters conflicting preferences (e.g., very low premium but also low deductible)</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>1. Enter low premium range 2. Enter low deductible preference 3. Enter low OOP maximum 4. Submit for recommendations</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>System attempts to find best match; User is informed if no plans meet all criteria; Trade-offs are explained; Plans closest to preferences are shown; User can adjust preferences</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Edge</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>TC_ENR_102</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Verify medication input with brand name vs generic name</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Validate that system recognizes both brand and generic medication names</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>User can enter medications by brand or generic name</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>1. Enter brand name medication (e.g., Lipitor) 2. Verify recognition 3. Enter generic name (e.g., Atorvastatin) 4. Verify recognition</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>System recognizes both brand and generic names; System may show both names for clarity; Formulary information is accurate for both; User can search by either name</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>TC_ENR_103</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Verify duplicate medication prevention</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Validate that system prevents adding duplicate medications</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>User attempts to add same medication twice</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>1. Add medication to list 2. Attempt to add same medication again 3. Observe system behavior</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>System detects duplicate medication; User is notified that medication already exists in list; Duplicate is not added; User can update existing entry if needed</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>TC_ENR_104</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Verify medication dosage and frequency capture</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Validate that system captures medication dosage and frequency if required</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>User is entering medication details</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>1. Enter medication name 2. Enter dosage information 3. Enter frequency 4. Save medication</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>System captures dosage and frequency if required by business rules; Information is used for cost estimation if applicable; Data is stored with medication entry; User can update dosage/frequency later</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>TC_ENR_105</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Verify provider search by specialty</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Validate that users can search for providers by specialty type</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>User needs to find specialist of specific type</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>1. Navigate to provider search 2. Select specialty from dropdown (e.g., Cardiology, Dermatology) 3. Enter location 4. Search 5. Review results</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>System displays providers matching selected specialty; Results are filtered by specialty type; Provider credentials confirm specialty; User can select from specialty-specific results</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>TC_ENR_106</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Verify provider search with multiple filter criteria</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Validate that users can apply multiple filters to provider search</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>User wants to narrow provider search with multiple criteria</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>1. Enter provider specialty 2. Enter location/zip code 3. Select network status filter 4. Select accepting new patients filter 5. Search 6. Review results</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>System applies all filters to search; Results match all selected criteria; User can see which filters are active; User can remove filters to broaden search; Filter combinations work correctly</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>TC_ENR_107</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Verify plan comparison includes prescription drug coverage details</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Validate that drug coverage is detailed in plan comparison</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>User has entered medications; Comparison tool is open</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>1. Open comparison tool 2. Locate prescription drug coverage section 3. Review drug coverage details</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>Drug coverage details are shown for each plan; Formulary tier for user's medications is displayed; Co-pay or coinsurance for each tier is shown; Coverage restrictions (prior auth, step therapy) are indicated; User can compare drug costs across plans</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>TC_ENR_108</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Verify plan comparison includes network size information</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Validate that network size/breadth is indicated in comparison</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>User is comparing plans</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>1. Open comparison tool 2. Locate network information section 3. Review network size details</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>Network size is indicated (e.g., number of providers, network type); User can understand relative network breadth; User's selected providers' status is shown; Network adequacy is clear for decision-making</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>TC_ENR_109</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Verify plan details include Summary of Benefits and Coverage (SBC)</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Validate that users can access official SBC document for each plan</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>User is reviewing plan details</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>1. View plan details 2. Locate SBC link or download option 3. Access SBC document</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>SBC document is available for each plan; Document is in standard format; User can view or download SBC; SBC includes all required information per ACA regulations</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>Compliance</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>TC_ENR_110</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Verify plan enrollment eligibility validation</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Validate that system verifies user eligibility for selected plan</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>User attempts to enroll in a plan</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>1. Select plan 2. Proceed to enrollment 3. System validates eligibility 4. Observe result</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>System validates user eligibility for selected plan; Eligibility criteria are checked (age, location, employment status, etc.); User is notified if ineligible; Eligible users can proceed with enrollment</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>TC_ENR_111</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Verify special enrollment period validation</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Validate that system enforces enrollment period rules</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>User attempts to enroll outside open enrollment period</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>1. Access enrollment outside open enrollment 2. Attempt to enroll 3. Observe system behavior</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>System enforces enrollment period rules; User is informed of enrollment period restrictions; Special enrollment period qualifying events are checked; User can proceed only if eligible; Appropriate messaging guides user</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>Compliance</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>TC_ENR_112</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Verify dependent enrollment support</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Validate that users can enroll dependents along with primary member</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>User wants to enroll dependents</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>1. Start enrollment 2. Add dependent information 3. Select plan for family 4. Review family coverage details 5. Submit enrollment</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>System supports dependent enrollment; User can add multiple dependents; Family coverage options are shown; Costs reflect family enrollment; All dependents are included in enrollment submission</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>TC_ENR_113</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Verify age-based plan eligibility (Medicare age)</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Validate that system handles age-based plan eligibility correctly</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>User is 65 or older (Medicare eligible age)</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>1. Enter date of birth indicating Medicare eligibility 2. Proceed with enrollment 3. View available plans</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>System recognizes Medicare eligibility; Appropriate plans are shown (Medicare Advantage, Supplement, etc.); Non-eligible plans are filtered out; User receives appropriate guidance</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Edge</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>TC_ENR_114</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Verify plan effective date display and selection</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Validate that plan effective date is clearly communicated</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>User is enrolling in a plan</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>1. Select plan 2. Proceed to enrollment 3. View effective date information 4. Confirm enrollment</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>Plan effective date is clearly displayed; User understands when coverage begins; Effective date follows business rules (e.g., first of month); User confirms understanding of effective date</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>TC_ENR_115</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Verify premium payment method selection</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Validate that users can select payment method for premiums</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>User is completing enrollment</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>1. Proceed to payment section 2. View payment method options 3. Select payment method (bank account, credit card, payroll deduction) 4. Enter payment details 5. Confirm</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>Multiple payment methods are available; User can select preferred method; Payment information is collected securely; Payment setup is confirmed; User receives payment schedule information</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>TC_ENR_116</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Verify integration with existing member account</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Validate that enrollment integrates with existing member account if applicable</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>User is existing member renewing or changing plans</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>1. Login with existing credentials 2. Start enrollment 3. Verify existing information is pre-populated 4. Update as needed 5. Complete enrollment</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>System recognizes existing member; Existing information is pre-populated; User can update information; Enrollment updates existing account; Continuity of member ID and history is maintained</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>TC_ENR_117</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Verify notification preferences capture</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Validate that system captures user's communication preferences</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>User is completing enrollment</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>1. Navigate to notification preferences 2. Select preferred communication channels (email, SMS, mail) 3. Select notification types 4. Save preferences</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>System captures communication preferences; User can select multiple channels; Preferences are saved with member profile; User can update preferences later; Preferences are honored for future communications</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>TC_ENR_118</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Verify terms and conditions acceptance</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Validate that user must accept terms and conditions before enrollment</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>User is completing enrollment</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>1. Proceed to final enrollment step 2. Locate terms and conditions 3. Review terms 4. Accept terms 5. Submit enrollment</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>Terms and conditions are presented; User must explicitly accept; Enrollment cannot proceed without acceptance; Acceptance is recorded with timestamp; Terms are accessible for future reference</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>Compliance</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>TC_ENR_119</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Verify privacy policy acknowledgment</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Validate that user acknowledges privacy policy</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>User is completing enrollment</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>1. Locate privacy policy 2. Review privacy policy 3. Acknowledge privacy policy 4. Proceed with enrollment</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>Privacy policy is presented; User must acknowledge; HIPAA notice of privacy practices is included; Acknowledgment is recorded; Policy is accessible for future reference</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>Compliance</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>TC_ENR_120</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Verify system handles special characters in user input fields</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Validate that system properly handles special characters across all input fields</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>User enters data with special characters</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>1. Enter name with special characters (e.g., O'Brien, José) 2. Enter address with special characters 3. Submit data 4. Verify proper storage and display</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>System accepts valid special characters; Data is stored correctly; Data displays correctly throughout application; No encoding issues occur; International characters are supported</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Edge</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
